--- a/Current Ontario MPPs & How They Vote..xlsx
+++ b/Current Ontario MPPs & How They Vote..xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3385" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="1071">
   <si>
     <t>MPP Name</t>
   </si>
@@ -3203,7 +3203,7 @@
     <t>OAC · Display Settings</t>
   </si>
   <si>
-    <t>Controls what the public MPP tracker shows. Data stays in the other tabs — this only toggles visibility.</t>
+    <t>Controls what the public MPP tracker shows. Data stays in the other tabs — this only toggles visibility for fields and which bills appear in the filters.</t>
   </si>
   <si>
     <t>Field</t>
@@ -3234,6 +3234,12 @@
   </si>
   <si>
     <t>Party voting alignment %</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Featured filter / campaign chip</t>
   </si>
 </sst>
 </file>
@@ -3245,7 +3251,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -3403,33 +3409,27 @@
     </font>
     <font>
       <b/>
-      <sz val="24.0"/>
-      <color rgb="FF0E0E0E"/>
-      <name val="Helvetica Neue"/>
+      <sz val="18.0"/>
+      <color rgb="FF0E121D"/>
+      <name val="Calibri"/>
     </font>
     <font/>
     <font>
-      <i/>
       <sz val="12.0"/>
-      <color rgb="FF757575"/>
-      <name val="Helvetica Neue"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12.0"/>
-      <color rgb="FF0E0E0E"/>
-      <name val="Helvetica Neue"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="12.0"/>
-      <color rgb="FFA60916"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF0E0E0E"/>
-      <name val="Helvetica Neue"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3495,24 +3495,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEBC36"/>
-        <bgColor rgb="FFFEBC36"/>
+        <fgColor rgb="FF181E2A"/>
+        <bgColor rgb="FF181E2A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE5EA"/>
-        <bgColor rgb="FFFEE5EA"/>
+        <fgColor rgb="FFFDDADB"/>
+        <bgColor rgb="FFFDDADB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F1E7"/>
-        <bgColor rgb="FFF5F1E7"/>
+        <fgColor rgb="FFD5FDE1"/>
+        <bgColor rgb="FFD5FDE1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="7">
     <border/>
     <border>
       <left/>
@@ -3554,93 +3554,35 @@
       <left style="thin">
         <color rgb="FF9A9A9A"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FF9A9A9A"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF9A9A9A"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFC7CBD3"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF9A9A9A"/>
+        <color rgb="FFC7CBD3"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFC7CBD3"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFC7CBD3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD5D5D5"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5D5D5"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9A9A9A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5D5D5"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD5D5D5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD5D5D5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD5D5D5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5D5D5"/>
+        <color rgb="FFC7CBD3"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3769,42 +3711,28 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="2" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="29" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="29" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="6" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="2" fillId="6" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="29" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="29" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="6" fillId="11" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="6" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="11" fillId="11" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="6" fillId="12" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="11" fillId="6" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="12" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="6" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="13" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="13" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="6" fillId="13" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23292,56 +23220,133 @@
       <c r="A2" s="57" t="s">
         <v>1058</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="56"/>
     </row>
     <row r="3">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="59" t="s">
         <v>1059</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="59" t="s">
         <v>1060</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="59" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="60" t="s">
         <v>1062</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="61" t="s">
         <v>1063</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="60" t="s">
         <v>1064</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="60" t="s">
         <v>1065</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="61" t="s">
         <v>1063</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="60" t="s">
         <v>1066</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="60" t="s">
         <v>1067</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="61" t="s">
         <v>1063</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="60" t="s">
         <v>1068</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="s">
+        <v>659</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="s">
+        <v>660</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="s">
+        <v>663</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="s">
+        <v>664</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="s">
+        <v>661</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="s">
+        <v>662</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="s">
+        <v>657</v>
+      </c>
+      <c r="B14" s="62" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>1070</v>
       </c>
     </row>
   </sheetData>

--- a/Current Ontario MPPs & How They Vote..xlsx
+++ b/Current Ontario MPPs & How They Vote..xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="8wtjvtIy+jYxcBMk+eUvWQQ8edLFPxK1cpyVj9xa6oA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="ug9ZCfUo/DnGAYg7wvZLeZQ/CAaP4zjSoqNJqMaAOdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="1071">
   <si>
     <t>MPP Name</t>
   </si>
@@ -10006,11 +10006,7 @@
     <col customWidth="1" min="9" max="9" width="10.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="9.86"/>
-    <col customWidth="1" min="12" max="15" width="8.71"/>
-    <col customWidth="1" hidden="1" min="16" max="16" width="8.71"/>
-    <col customWidth="1" min="17" max="21" width="8.71"/>
-    <col customWidth="1" hidden="1" min="22" max="23" width="8.71"/>
-    <col customWidth="1" min="24" max="24" width="8.71"/>
+    <col customWidth="1" min="12" max="24" width="8.71"/>
     <col customWidth="1" min="25" max="25" width="9.86"/>
     <col customWidth="1" min="26" max="33" width="8.71"/>
     <col customWidth="1" min="34" max="34" width="13.57"/>
@@ -23274,7 +23270,7 @@
     </row>
     <row r="8">
       <c r="A8" s="60" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B8" s="62" t="s">
         <v>1069</v>
@@ -23285,7 +23281,7 @@
     </row>
     <row r="9">
       <c r="A9" s="60" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B9" s="62" t="s">
         <v>1069</v>
@@ -23296,7 +23292,7 @@
     </row>
     <row r="10">
       <c r="A10" s="60" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B10" s="62" t="s">
         <v>1069</v>
@@ -23307,7 +23303,7 @@
     </row>
     <row r="11">
       <c r="A11" s="60" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B11" s="62" t="s">
         <v>1069</v>
@@ -23318,7 +23314,7 @@
     </row>
     <row r="12">
       <c r="A12" s="60" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B12" s="62" t="s">
         <v>1069</v>
@@ -23329,7 +23325,7 @@
     </row>
     <row r="13">
       <c r="A13" s="60" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B13" s="62" t="s">
         <v>1069</v>
@@ -23340,12 +23336,23 @@
     </row>
     <row r="14">
       <c r="A14" s="60" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B14" s="62" t="s">
         <v>1069</v>
       </c>
       <c r="C14" s="60" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="60" t="s">
+        <v>664</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C15" s="60" t="s">
         <v>1070</v>
       </c>
     </row>

--- a/Current Ontario MPPs & How They Vote..xlsx
+++ b/Current Ontario MPPs & How They Vote..xlsx
@@ -9996,10 +9996,10 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="24.0"/>
-    <col customWidth="1" hidden="1" min="2" max="2" width="24.29"/>
-    <col customWidth="1" hidden="1" min="3" max="3" width="19.0"/>
-    <col customWidth="1" hidden="1" min="4" max="4" width="24.29"/>
-    <col customWidth="1" hidden="1" min="5" max="5" width="20.0"/>
+    <col customWidth="1" min="2" max="2" width="24.29"/>
+    <col customWidth="1" min="3" max="3" width="19.0"/>
+    <col customWidth="1" min="4" max="4" width="24.29"/>
+    <col customWidth="1" min="5" max="5" width="20.0"/>
     <col customWidth="1" min="6" max="6" width="14.0"/>
     <col customWidth="1" min="7" max="7" width="13.29"/>
     <col customWidth="1" hidden="1" min="8" max="8" width="9.29"/>

--- a/Current Ontario MPPs & How They Vote..xlsx
+++ b/Current Ontario MPPs & How They Vote..xlsx
@@ -10447,8 +10447,8 @@
       <c r="Y5" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="Z5" s="47" t="s">
-        <v>675</v>
+      <c r="Z5" s="41" t="s">
+        <v>670</v>
       </c>
       <c r="AA5" s="47" t="s">
         <v>675</v>

--- a/Current Ontario MPPs & How They Vote..xlsx
+++ b/Current Ontario MPPs & How They Vote..xlsx
@@ -10447,8 +10447,8 @@
       <c r="Y5" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="Z5" s="41" t="s">
-        <v>670</v>
+      <c r="Z5" s="47" t="s">
+        <v>675</v>
       </c>
       <c r="AA5" s="47" t="s">
         <v>675</v>
